--- a/naver-place-crawler/results_health/서구_PT.xlsx
+++ b/naver-place-crawler/results_health/서구_PT.xlsx
@@ -417,13 +417,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="49" customWidth="1" min="7" max="7"/>
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>바디소나타 헬스 PT 청라</t>
+          <t>테오짐 PT 청라점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>body_sonata@naver.com</t>
+          <t>teogym@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1404-7217</t>
+          <t>0507-1373-7578</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로586번길 15 청연프라자 10층</t>
+          <t>인천광역시 서구 청라커낼로 280 청라골든프라자 5층 505호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://2080ttt.wixsite.com/bodysonata</t>
+          <t>https://www.instagram.com/gymteogym</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1578</v>
+        <v>39</v>
       </c>
       <c r="Q2" t="n">
-        <v>1566</v>
+        <v>170</v>
       </c>
       <c r="R2" t="n">
-        <v>3144</v>
+        <v>209</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>38782467</t>
+          <t>1814118302</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38782467</t>
+          <t>https://m.place.naver.com/place/1814118302</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>힙디자인팩토리 PT 검단 신도시점</t>
+          <t>프레임짐 헬스 PT 검단</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>natural_sehun@naver.com</t>
+          <t>framegym_yu@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1384-6150</t>
+          <t>0507-1352-9688</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음대로 459 파라곤프라자 3층 힙디자인팩토리</t>
+          <t>인천광역시 서구 검단로 480 리치웰프라자 10층 프레임짐</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/natural_sehun/223137384574</t>
+          <t>https://blog.naver.com/framegym_yu</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>211</v>
+        <v>92</v>
       </c>
       <c r="Q3" t="n">
-        <v>1660</v>
+        <v>317</v>
       </c>
       <c r="R3" t="n">
-        <v>1871</v>
+        <v>409</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1945940640</t>
+          <t>1741458759</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1945940640</t>
+          <t>https://m.place.naver.com/place/1741458759</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>올나잇 피트니스 가정점 헬스&amp;PT</t>
+          <t>웰무브 근골격운동센터 청라점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rdx329@naver.com</t>
+          <t>wellmove_ex@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1475-6636</t>
+          <t>0507-1423-9397</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 451 벨라미센텀시티2차 13층 1320호</t>
+          <t>인천광역시 서구 청라라임로 71 8층 808호, 809호 웰무브 근골격운동센터</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/all.night_3</t>
+          <t>https://www.instagram.com/wellmove_1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1742</v>
+        <v>52</v>
       </c>
       <c r="Q4" t="n">
-        <v>536</v>
+        <v>144</v>
       </c>
       <c r="R4" t="n">
-        <v>2278</v>
+        <v>196</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,51 +824,51 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1898172914</t>
+          <t>1594642239</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1898172914</t>
+          <t>https://m.place.naver.com/place/1594642239</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>터닝포인트짐 헬스 PT&amp;필라테스 청라점</t>
+          <t>인싸짐 가좌점 24시연중무휴 PT 헬스장</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>tpgym6@naver.com</t>
+          <t>wjdguss1045@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1340-9221</t>
+          <t>0507-1376-3818</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로 594 비전프라자 10층</t>
+          <t>인천광역시 서구 원적로 100 지하2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.tpgymcheongna.kr</t>
+          <t>http://pf.kakao.com/_SxiUZG</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>416</v>
+        <v>1189</v>
       </c>
       <c r="Q5" t="n">
-        <v>3424</v>
+        <v>748</v>
       </c>
       <c r="R5" t="n">
-        <v>3840</v>
+        <v>1937</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>37450365</t>
+          <t>1748758798</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37450365</t>
+          <t>https://m.place.naver.com/place/1748758798</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -940,34 +940,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>좋은습관 PT STUDIO 청라</t>
+          <t>더피티짐 헬스&amp;PT 검단점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>goodhabit_ch@naver.com</t>
+          <t>volleystar1@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1435-9902</t>
+          <t>0507-1448-1037</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 2층 청라PT 좋은습관</t>
+          <t>인천광역시 서구 이음대로 463 센트럴시티 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goodhabit_ch</t>
+          <t>https://thepit.creatorlink.net</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -988,7 +988,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>546</v>
+        <v>240</v>
       </c>
       <c r="Q6" t="n">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="R6" t="n">
-        <v>805</v>
+        <v>506</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,56 +1012,56 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1404702049</t>
+          <t>1631976018</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1404702049</t>
+          <t>https://m.place.naver.com/place/1631976018</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>카우짐24시 서구청역점</t>
+          <t>하루50분 PT필라테스 루원시티점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>coco951215@naver.com</t>
+          <t>rladnwjd802@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1376-7926</t>
+          <t>0507-1481-4556</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 서구 탁옥로51번길 11 702호, 703호, 704호</t>
+          <t>인천광역시 서구 봉오대로 255 눈담봄 5층 507,8호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/cowgymseogu</t>
+          <t>https://blog.naver.com/rladnwjd802</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1087,17 +1087,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1021</v>
+        <v>226</v>
       </c>
       <c r="Q7" t="n">
-        <v>324</v>
+        <v>195</v>
       </c>
       <c r="R7" t="n">
-        <v>1345</v>
+        <v>421</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1106839652</t>
+          <t>1001087379</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1106839652</t>
+          <t>https://m.place.naver.com/place/1001087379</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1128,34 +1128,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>더피티짐 프리미엄 루원시티점</t>
+          <t>터닝포인트짐</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gktk1877@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>ksmturning@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>tpgym7777@nate.com</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1375-9681</t>
+          <t>0507-1340-0803</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오대로 270 302동 상가B 110~112호 (파리바게트 위층)</t>
+          <t>인천광역시 서구 중봉대로 594 6층 601호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gktk1877</t>
+          <t>https://turningpointgym.kr/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1185,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>121</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>178</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>299</v>
+        <v>5</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,61 +1204,61 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1650465158</t>
+          <t>1679398325</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1650465158</t>
+          <t>https://m.place.naver.com/place/1679398325</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>전칠성의 히어로짐 헬스 PT 그룹PT 청라점</t>
+          <t>검단플렉스짐PT 완정점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>whitemurder@naver.com</t>
+          <t>flexpt@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1323-9682</t>
+          <t>0507-1328-8130</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 7-11 퍼스트타워 7층 전칠성의 히어로짐 청라점</t>
+          <t>인천광역시 서구 원당대로 676 3층 304호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/whitemurder/224211279556</t>
+          <t>https://m.blog.naver.com/PostList.nhn?blogId=flexpt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1275,17 +1279,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="Q9" t="n">
-        <v>495</v>
+        <v>1269</v>
       </c>
       <c r="R9" t="n">
-        <v>668</v>
+        <v>1349</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,51 +1298,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1613152191</t>
+          <t>1127062086</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1613152191</t>
+          <t>https://m.place.naver.com/place/1127062086</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>더피티짐 헬스&amp;PT 검단점</t>
+          <t>모앤핏 여성전용 헬스&amp;PT 검단점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>awer0411@naver.com</t>
+          <t>moanfit1@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1448-1037</t>
+          <t>0507-1497-2153</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음대로 463 센트럴시티 4층</t>
+          <t>인천광역시 서구 발산로 27 507호~511호 모앤핏</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://thepit.creatorlink.net</t>
+          <t>https://booking.naver.com/booking/13/bizes/1557337</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1348,12 +1352,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1364,7 +1368,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1373,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>240</v>
+        <v>89</v>
       </c>
       <c r="Q10" t="n">
-        <v>266</v>
+        <v>334</v>
       </c>
       <c r="R10" t="n">
-        <v>506</v>
+        <v>423</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1392,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1631976018</t>
+          <t>2004609184</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1631976018</t>
+          <t>https://m.place.naver.com/place/2004609184</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1410,29 +1414,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>청라재활PT 피지오쏭운동센터</t>
+          <t>하루50분 PT필라테스 청라점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>l2037002@naver.com</t>
+          <t>rladnwjd802@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1399-9872</t>
+          <t>0507-1311-9363</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 11 1동 10층 1010호</t>
+          <t>인천광역시 서구 청라라임로122번길 16-1 1층 101호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/l2037002</t>
+          <t>https://blog.naver.com/rladnwjd802</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1467,13 +1471,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>138</v>
+        <v>248</v>
       </c>
       <c r="Q11" t="n">
-        <v>285</v>
+        <v>245</v>
       </c>
       <c r="R11" t="n">
-        <v>423</v>
+        <v>493</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1486,6107 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1128948740</t>
+          <t>1947556374</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1128948740</t>
+          <t>https://m.place.naver.com/place/1947556374</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>핏트레인 PT 청라</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>fittrain_@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1363-5598</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로72번길 7-31 205호, 206호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fittrain_</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>86</v>
+      </c>
+      <c r="R12" t="n">
+        <v>135</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1976065832</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1976065832</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>제니의써킷짐</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>fcchh7023@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1327-9857</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 봉화로 52 벧엘빌딩 2층</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jeny_gym2015?igsh=ZjFtOXYzYTJ2Z25l</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>50</v>
+      </c>
+      <c r="R13" t="n">
+        <v>96</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1181295362</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1181295362</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>오유짐</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>oyugym@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1357-8173</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 이음5로 66 서영아너시티1차 7층 702호~704</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/oyugym</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>93</v>
+      </c>
+      <c r="R14" t="n">
+        <v>181</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>576457172</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/576457172</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>하이브짐 헬스 PT 검단점</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>hivegym2021@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1491-1459</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 원당대로 841 7층 701호-704호</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hivegym2021</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>3122</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1432</v>
+      </c>
+      <c r="R15" t="n">
+        <v>4554</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1556816158</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1556816158</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>더피티짐 프리미엄 루원시티점</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>gktk1877@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1375-9681</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 봉오대로 270 302동 상가B 110~112호 (파리바게트 위층)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gktk1877</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>178</v>
+      </c>
+      <c r="R16" t="n">
+        <v>299</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1650465158</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1650465158</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>리커버리짐 가정점</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>rcv0715@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1393-0213</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 봉오재3로110번길 7 504호</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rcv0715</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>103</v>
+      </c>
+      <c r="R17" t="n">
+        <v>197</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1133026207</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1133026207</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>좋은습관 PT STUDIO 청라</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>goodhabit_ch@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1435-9902</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 2층 청라PT 좋은습관</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/goodhabit_ch</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>546</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>259</v>
+      </c>
+      <c r="R18" t="n">
+        <v>805</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1404702049</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1404702049</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>강자존 리햅 1대1 PT샵 루원시티점</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>tjdwnsldlek@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1365-0715</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 봉오재3로 116 3층 306호 강자존 리햅 1대1 PT샵 루원시티점</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/tjdwnsldlek/224143719751</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>69</v>
+      </c>
+      <c r="R19" t="n">
+        <v>164</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>2001611714</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2001611714</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>청라PT&amp;몸짱스쿨</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>kura7792@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1343-9683</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로586번길 9-11 매그놀리아오피스텔 3층 몸짱스쿨</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kura7792</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>110</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>219</v>
+      </c>
+      <c r="R20" t="n">
+        <v>329</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>37547267</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37547267</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>태나핏</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>anth14@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>032-566-7939</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 승학로 515 301호, 302호, 305호</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/anth14</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1909</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1927</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>35623573</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35623573</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>청라PT 바른몸피트니스 1호점</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>barunmom_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1340-7437</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라루비로 93 루비타워 4층</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/booking/12/bizes/815141</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>697</v>
+      </c>
+      <c r="R22" t="n">
+        <v>997</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1059514904</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1059514904</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>슬릭부스트 루원시티점</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>sleekboost__lu1@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1390-4983</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 새오개로111번안길 26 3층</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sleekboost_lu1/</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>312</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>234</v>
+      </c>
+      <c r="R23" t="n">
+        <v>546</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1634343801</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1634343801</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>데일리 무브먼트 재활&amp;PT</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>daily_movement_@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1491-1050</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 이음5로 60 3층 304호 데일리 무브먼트</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/daily_movement_</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>42</v>
+      </c>
+      <c r="R24" t="n">
+        <v>67</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>2000481326</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2000481326</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>팀윤짐 PT 검단점</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>daalarm@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1318-4581</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 이음5로 24 쓰리엠타워 3층 팀윤짐 검단 8호점</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/daalarm</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>144</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>409</v>
+      </c>
+      <c r="R25" t="n">
+        <v>553</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1110145168</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1110145168</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>루원짐 PT 루원시티점</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>luwongym@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청중로478번길 24 3층</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/luwongym</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>110</v>
+      </c>
+      <c r="R26" t="n">
+        <v>187</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1538350747</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1538350747</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>위크짐 헬스&amp;PT 검단사거리점</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>weekgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1389-7739</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 완정로 151-1 왕길빌딩 4층</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/weekgym</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>268</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>389</v>
+      </c>
+      <c r="R27" t="n">
+        <v>657</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1265962914</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1265962914</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CM 재활PT &amp; 필라테스 검단점</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>jcm9909@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1334-0270</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 이음5로 34 제일프라자 405호</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jcm9909</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>156</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>191</v>
+      </c>
+      <c r="R28" t="n">
+        <v>347</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1045251150</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1045251150</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>여름필라테스 루원시티점</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>summer3-@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1420-9515</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 가정로 375 301호</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/summer3-</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>417</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>609</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1026</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1993174819</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1993174819</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>청라헬스장 킹짐7호점 24시 헬스 PT</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>kinggym7@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1410-9579</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로 85 C동 지하1층 101호</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kinggym7</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>219</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>927</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1146</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>2068038054</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2068038054</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>올나잇 피트니스 가정점 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>rdx329@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1475-6636</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 가정로 451 벨라미센텀시티2차 13층 1320호</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/all.night_3</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>1744</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>536</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2280</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1898172914</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1898172914</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>힙디자인팩토리 PT 검단 신도시점</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>natural_sehun@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1384-6150</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 이음대로 459 파라곤프라자 3층 힙디자인팩토리</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/natural_sehun/223137384574</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>212</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1686</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1898</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1945940640</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1945940640</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>조스짐 2호점</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>bonanza0917@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1417-9682</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 가정로 437 301B동 109호 조스짐</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bonanza0917</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>125</v>
+      </c>
+      <c r="R33" t="n">
+        <v>275</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1391522406</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1391522406</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>터닝포인트짐 헬스 PT&amp;필라테스 청라점</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>tpgym6@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1340-9221</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로 594 비전프라자 10층</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://www.tpgymcheongna.kr</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>417</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3429</v>
+      </c>
+      <c r="R34" t="n">
+        <v>3846</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>37450365</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37450365</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>마스터 와이짐 PT 청라점</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>master_y_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로288번길 10 더스페이스타워 305호</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/master__y_gym</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>356</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>494</v>
+      </c>
+      <c r="R35" t="n">
+        <v>850</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1200262369</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1200262369</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>트리니티 피트니스 헬스 PT 청라</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>trinity_fit@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 크리스탈로 84 청라 레이크가든 빌딩 5층</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/trinity_fit/</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>919</v>
+      </c>
+      <c r="R36" t="n">
+        <v>999</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1044334882</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1044334882</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>업라이트 피트니스</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>uprightfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1392-7187</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 한들로 74 7층 업라이트 피트니스</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/uprightfitness</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>364</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>453</v>
+      </c>
+      <c r="R37" t="n">
+        <v>817</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1673143477</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1673143477</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>어라운드 헬스&amp;PT 청라</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>aroundgym_1@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1327-9593</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로586번길 9-4 3층 307호 어라운드 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/aroundgym_1</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>393</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>286</v>
+      </c>
+      <c r="R38" t="n">
+        <v>679</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1698654705</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1698654705</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>청라 피트니스비에이 PT&amp;헬스</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>fitnessba@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1359-0563</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 푸른로16번길 15 1층</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fitnessba</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>61</v>
+      </c>
+      <c r="R39" t="n">
+        <v>90</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1922697320</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1922697320</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>크로스핏 피포피 가정점</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>bow14674@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1345-3994</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 새오개로111번안길 19-1 지하 1층</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bow14674</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>84</v>
+      </c>
+      <c r="R40" t="n">
+        <v>139</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1971300109</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1971300109</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>마침.여기,피티스튜디오</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>su2kimc@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 이음대로 388 ABM타워 3층 303호</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/su2kimc</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>342</v>
+      </c>
+      <c r="R41" t="n">
+        <v>436</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1381559698</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1381559698</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>록 피트니스 R.O.K 헬스&amp;PT 가정점</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>rok03903@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 염곡로464번길 23 엔시티타워 7층</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rok03903</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>727</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1173</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1900</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1475425565</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1475425565</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>레인헬스PT 서구청점</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>sonyeopps@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1487-0787</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 탁옥로 37 2층 201호</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sonyeopps</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>125</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>168</v>
+      </c>
+      <c r="R43" t="n">
+        <v>293</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1799609656</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1799609656</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>캐스캐이드 PT 청라점</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>cascadept@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1311-2169</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라루비로134번길 18 1층</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://casecadept.homebuilder.co.kr</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>197</v>
+      </c>
+      <c r="R44" t="n">
+        <v>283</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1173494121</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1173494121</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>찐바디핏</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>din32@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1377-4737</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 크리스탈로 78 엘림존 301호</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/din32</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>146</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>443</v>
+      </c>
+      <c r="R45" t="n">
+        <v>589</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1039953052</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1039953052</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>피지컬뷰티짐 청라점 PT &amp; 헬스</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>physicalbeauty@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1358-0655</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로 270 2층 피지컬뷰티짐 청라점</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/피지컬뷰티</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>511</v>
+      </c>
+      <c r="R46" t="n">
+        <v>599</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1693588410</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1693588410</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>클래식짐청라PT</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>classicgym-@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1350-6909</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로161번길 1 2층</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>2</v>
+      </c>
+      <c r="R47" t="n">
+        <v>29</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>2057021183</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2057021183</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>어테인휘트니스 헬스&amp;PT 석남점</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>attain_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1337-3765</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 길주로 101-1 투썸플레이스건물 4층</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/attain.fitness1/</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>353</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>519</v>
+      </c>
+      <c r="R48" t="n">
+        <v>872</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1639913680</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1639913680</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>펌퍼스짐 헬스&amp;PT 청라</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>pumper_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1476-9054</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로 110 파이낸스센터 6층</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pumpers_gym?igsh=MXJueDAwamF5cWpheQ%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>256</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>258</v>
+      </c>
+      <c r="R49" t="n">
+        <v>514</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1828279952</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1828279952</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>엘핏 청라점</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>lemongym-cn@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1428-5104</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 옥빛로13번길 3 1층 엘핏</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/lemongym-cn</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>89</v>
+      </c>
+      <c r="R50" t="n">
+        <v>154</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1196898702</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1196898702</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>터닝포인트짐 헬스 PT 가좌점</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>turningpointgym_gajw@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>032-576-1365</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 원적로 85 우신프라자 B1층 B01~B02호</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/turningpointgym_gajw</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>538</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1549</v>
+      </c>
+      <c r="R51" t="n">
+        <v>2087</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1588426455</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1588426455</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>데이온 휘트니스 헬스&amp;PT 검단1호점</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>day_on11@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1466-1299</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 바리미로5번길 8 검단골든스퀘어 7층 전체</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dayon_fitness/?hl=ko</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>1312</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1058</v>
+      </c>
+      <c r="R52" t="n">
+        <v>2370</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1249225301</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1249225301</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>젠틀레이디짐 PT&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>gentlelady_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1384-8303</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로288번길 26 상가동 103동 324호</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gentlelady_gym</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>532</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>620</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1152</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1188954884</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1188954884</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>피트니스13월 불로점</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>fitnessmonth13@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1480-3383</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 검단로 759 2층 201, 202, 203호</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fitnessmonth13/</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>164</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>178</v>
+      </c>
+      <c r="R54" t="n">
+        <v>342</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1650154499</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1650154499</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>5150피트니스 헬스&amp;필라테스&amp;PT 검단점</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>jgym0202@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1413-1819</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 서곶로 788 홀리랜드 3층 5150피트니스 검단점</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jgym0202</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>562</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1525</v>
+      </c>
+      <c r="R55" t="n">
+        <v>2087</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>37434686</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37434686</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>카우짐24시 서구청역점</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>coco951215@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1376-7926</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 탁옥로51번길 11 702호, 703호, 704호</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://link.inpock.co.kr/cowgymseogu</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>1020</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>324</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1344</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1106839652</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1106839652</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>드라이짐 헬스&amp;PT 검단점</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>drygym@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1350-0887</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 이음5로 72 국제프라자 7층 드라이짐</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/drygym</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>1523</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1389</v>
+      </c>
+      <c r="R57" t="n">
+        <v>2912</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1566516040</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1566516040</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>피타짐 서구청역점 24시 헬스PT</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>fita_07@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1389-6929</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 탁옥로98번길 1 4층</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_Sraxin/chat</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>132</v>
+      </c>
+      <c r="R58" t="n">
+        <v>215</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>2094767341</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2094767341</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>하루50분 PT필라테스 청라4호점</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>rladnwjd802@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1423-7258</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로 78 4층 405호</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rladnwjd802</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>129</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>123</v>
+      </c>
+      <c r="R59" t="n">
+        <v>252</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>2038838362</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2038838362</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>이음핏 PT 스튜디오</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>eumfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1433-0360</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 서곶로 285 4층</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/eumfit</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>41</v>
+      </c>
+      <c r="R60" t="n">
+        <v>141</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1260849924</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1260849924</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1:1 개인PT샵 팻번</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>gbw21@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>032-246-2158</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 건지로 375 5층 팻번</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gbw21</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>148</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>260</v>
+      </c>
+      <c r="R61" t="n">
+        <v>408</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1216515131</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1216515131</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>청년피티 청라점</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>cnpt3455@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1434-3455</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로 610 3층</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://cnptoffical.qshop.ai/</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>433</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>236</v>
+      </c>
+      <c r="R62" t="n">
+        <v>669</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1293398871</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1293398871</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>머슬피플 피트니스 헬스 PT 청라</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>kdkkdk8399@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1339-0000</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로72번길 23 701호, 702호</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kdkkdk8399</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>370</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1162</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1532</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1197174862</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1197174862</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>바디소나타 헬스 PT 청라</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>body_sonata@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1404-7217</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로586번길 15 청연프라자 10층</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://2080ttt.wixsite.com/bodysonata</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>1580</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1579</v>
+      </c>
+      <c r="R64" t="n">
+        <v>3159</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>38782467</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38782467</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>휘트니스칸 헬스&amp;PT&amp;골프&amp;요가&amp;필라테스 마전점</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>kann004@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1365-4330</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 완정로 70 영남탑스빌아파트 상가 401호</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://fitnesskann.com/</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>1301</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>610</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1911</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1220498447</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1220498447</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>세인트피트니스 청라점 PT&amp;헬스</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>soccerkkw2@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1354-4659</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로 71 진영메디피아 9층 905호</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/soccerkkw2</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>948</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>916</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1864</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1577621981</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1577621981</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>엑스짐 신현점</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>xgym01@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1402-2033</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 가정로 419 . 4층 401호, 402호(신현동)</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/x_gym_can?igsh=NGxodHQ0b2FlbWFr</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>430</v>
+      </c>
+      <c r="R67" t="n">
+        <v>550</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1413141073</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1413141073</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>마이짐 PT 청라점</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>better__life@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1378-3868</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로612번길 10-20 6층 마이짐</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mygym_pt_official?igsh=dGMxNWw2eG40MWtx</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>396</v>
+      </c>
+      <c r="R68" t="n">
+        <v>453</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1099553298</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1099553298</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>사이언스핏 PT필라 청라점</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>sciencefit@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1487-2044</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로612번길 10-8 반안프라자 401호, 402호, 403호</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/science_fit__</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>762</v>
+      </c>
+      <c r="R69" t="n">
+        <v>867</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1329193780</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1329193780</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>고트트레이닝센터</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>goat_psvt@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1330-9573</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 서곶로 746 3층</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/goat_psvt</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>276</v>
+      </c>
+      <c r="R70" t="n">
+        <v>294</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1362765821</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1362765821</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>청라스포츠센터 헬스 PT</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>uzwuzw@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1300-4100</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로 99 지젤엠 A동 4층</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/csc_training_center</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>2832</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>1229</v>
+      </c>
+      <c r="R71" t="n">
+        <v>4061</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1213983093</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1213983093</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>플러스짐 24시 헬스 PT 검단점</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>plusgymgeomdan@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1362-0454</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 검단로 455 검단KB빌딩 3층 301, 302호</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/plusgymgeomdan</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>528</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>617</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1145</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>2090890779</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2090890779</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>가좌동 1:1 PT 글램핏</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>glamfit_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1328-4459</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 장고개로337번길 7 4층 401호</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sTCuqroe</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>112</v>
+      </c>
+      <c r="R73" t="n">
+        <v>188</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1111122713</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1111122713</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>GN짐 헬스&amp;PT 검단점</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>gn_gym-@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1458-7938</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 완정로 148-1 6층</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_tkdBn</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>125</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>581</v>
+      </c>
+      <c r="R74" t="n">
+        <v>706</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>2036025124</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2036025124</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>청라PT 바른몸피트니스 2호점</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>barunmom_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1413-7437</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로612번길 10-22 604, 605호</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/booking/12/bizes/1418130</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>213</v>
+      </c>
+      <c r="R75" t="n">
+        <v>288</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>2032271782</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2032271782</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>커넥트바디 재활&amp;PT 청라점</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>connect-body@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1380-8515</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 보석로12번안길 35 1층</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/connect-body/223458723996</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>157</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>451</v>
+      </c>
+      <c r="R76" t="n">
+        <v>608</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1346258755</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1346258755</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/서구_PT.xlsx
+++ b/naver-place-crawler/results_health/서구_PT.xlsx
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>테오짐 PT 청라점</t>
+          <t>올나잇 피트니스 가정점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>teogym@naver.com</t>
+          <t>rdx329@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1373-7578</t>
+          <t>0507-1475-6636</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로 280 청라골든프라자 5층 505호</t>
+          <t>인천광역시 서구 가정로 451 벨라미센텀시티2차 13층 1320호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gymteogym</t>
+          <t>https://www.instagram.com/all.night_3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>39</v>
+        <v>1746</v>
       </c>
       <c r="Q2" t="n">
-        <v>170</v>
+        <v>537</v>
       </c>
       <c r="R2" t="n">
-        <v>209</v>
+        <v>2283</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1814118302</t>
+          <t>1898172914</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1814118302</t>
+          <t>https://m.place.naver.com/place/1898172914</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,34 +658,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>프레임짐 헬스 PT 검단</t>
+          <t>바디소나타 헬스 PT 청라</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>framegym_yu@naver.com</t>
+          <t>body_sonata@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1352-9688</t>
+          <t>0507-1404-7217</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 서구 검단로 480 리치웰프라자 10층 프레임짐</t>
+          <t>인천광역시 서구 중봉대로586번길 15 청연프라자 10층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/framegym_yu</t>
+          <t>https://2080ttt.wixsite.com/bodysonata</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -706,22 +706,22 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>92</v>
+        <v>1581</v>
       </c>
       <c r="Q3" t="n">
-        <v>317</v>
+        <v>1583</v>
       </c>
       <c r="R3" t="n">
-        <v>409</v>
+        <v>3164</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1741458759</t>
+          <t>38782467</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1741458759</t>
+          <t>https://m.place.naver.com/place/38782467</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>웰무브 근골격운동센터 청라점</t>
+          <t>하루50분 PT필라테스 청라4호점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>wellmove_ex@naver.com</t>
+          <t>rladnwjd802@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1423-9397</t>
+          <t>0507-1423-7258</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 71 8층 808호, 809호 웰무브 근골격운동센터</t>
+          <t>인천광역시 서구 청라에메랄드로 78 4층 405호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wellmove_1</t>
+          <t>https://blog.naver.com/rladnwjd802</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -805,17 +805,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>52</v>
+        <v>130</v>
       </c>
       <c r="Q4" t="n">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="R4" t="n">
-        <v>196</v>
+        <v>254</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1594642239</t>
+          <t>2038838362</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1594642239</t>
+          <t>https://m.place.naver.com/place/2038838362</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,34 +846,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>인싸짐 가좌점 24시연중무휴 PT 헬스장</t>
+          <t>머슬피플 피트니스 헬스 PT 청라</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>wjdguss1045@naver.com</t>
+          <t>kdkkdk8399@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1376-3818</t>
+          <t>0507-1339-0000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원적로 100 지하2층</t>
+          <t>인천광역시 서구 청라한내로72번길 23 701호, 702호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_SxiUZG</t>
+          <t>https://blog.naver.com/kdkkdk8399</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -894,7 +894,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1189</v>
+        <v>370</v>
       </c>
       <c r="Q5" t="n">
-        <v>748</v>
+        <v>1163</v>
       </c>
       <c r="R5" t="n">
-        <v>1937</v>
+        <v>1533</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1748758798</t>
+          <t>1197174862</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1748758798</t>
+          <t>https://m.place.naver.com/place/1197174862</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,34 +940,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>더피티짐 헬스&amp;PT 검단점</t>
+          <t>좋은습관 PT STUDIO 청라</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>volleystar1@naver.com</t>
+          <t>goodhabit_ch@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1448-1037</t>
+          <t>0507-1435-9902</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음대로 463 센트럴시티 4층</t>
+          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 2층 청라PT 좋은습관</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://thepit.creatorlink.net</t>
+          <t>https://blog.naver.com/goodhabit_ch</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -988,7 +988,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>240</v>
+        <v>547</v>
       </c>
       <c r="Q6" t="n">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="R6" t="n">
-        <v>506</v>
+        <v>806</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1631976018</t>
+          <t>1404702049</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1631976018</t>
+          <t>https://m.place.naver.com/place/1404702049</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>하루50분 PT필라테스 루원시티점</t>
+          <t>찐바디핏</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rladnwjd802@naver.com</t>
+          <t>din32@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1481-4556</t>
+          <t>0507-1377-4737</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오대로 255 눈담봄 5층 507,8호</t>
+          <t>인천광역시 서구 크리스탈로 78 엘림존 301호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rladnwjd802</t>
+          <t>https://blog.naver.com/din32</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>226</v>
+        <v>146</v>
       </c>
       <c r="Q7" t="n">
-        <v>195</v>
+        <v>443</v>
       </c>
       <c r="R7" t="n">
-        <v>421</v>
+        <v>589</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1001087379</t>
+          <t>1039953052</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1001087379</t>
+          <t>https://m.place.naver.com/place/1039953052</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1128,38 +1128,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>터닝포인트짐</t>
+          <t>트리니티 피트니스 헬스 PT 청라</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ksmturning@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>tpgym7777@nate.com</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1340-0803</t>
-        </is>
-      </c>
+          <t>trinity_fit@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로 594 6층 601호</t>
+          <t>인천광역시 서구 크리스탈로 84 청라 레이크가든 빌딩 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://turningpointgym.kr/</t>
+          <t>https://blog.naver.com/trinity_fit/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1189,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>918</v>
       </c>
       <c r="R8" t="n">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1196,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1679398325</t>
+          <t>1044334882</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1679398325</t>
+          <t>https://m.place.naver.com/place/1044334882</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1221,34 +1213,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>검단플렉스짐PT 완정점</t>
+          <t>모앤핏 여성전용 헬스&amp;PT 검단점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>flexpt@naver.com</t>
+          <t>moanfit1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1328-8130</t>
+          <t>0507-1497-2153</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원당대로 676 3층 304호</t>
+          <t>인천광역시 서구 발산로 27 507호~511호 모앤핏</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://m.blog.naver.com/PostList.nhn?blogId=flexpt</t>
+          <t>https://booking.naver.com/booking/13/bizes/1557337</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,17 +1271,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="Q9" t="n">
-        <v>1269</v>
+        <v>334</v>
       </c>
       <c r="R9" t="n">
-        <v>1349</v>
+        <v>423</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1290,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1127062086</t>
+          <t>2004609184</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1127062086</t>
+          <t>https://m.place.naver.com/place/2004609184</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1315,44 +1307,44 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>모앤핏 여성전용 헬스&amp;PT 검단점</t>
+          <t>젠틀레이디짐 PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>moanfit1@naver.com</t>
+          <t>gentlelady_gym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1497-2153</t>
+          <t>0507-1384-8303</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 서구 발산로 27 507호~511호 모앤핏</t>
+          <t>인천광역시 서구 청라커낼로288번길 26 상가동 103동 324호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/13/bizes/1557337</t>
+          <t>https://blog.naver.com/gentlelady_gym</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1377,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>89</v>
+        <v>532</v>
       </c>
       <c r="Q10" t="n">
-        <v>334</v>
+        <v>622</v>
       </c>
       <c r="R10" t="n">
-        <v>423</v>
+        <v>1154</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1384,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2004609184</t>
+          <t>1188954884</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2004609184</t>
+          <t>https://m.place.naver.com/place/1188954884</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1414,29 +1406,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>하루50분 PT필라테스 청라점</t>
+          <t>피트니스13월 불로점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>rladnwjd802@naver.com</t>
+          <t>fitnessmonth13@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1311-9363</t>
+          <t>0507-1480-3383</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로122번길 16-1 1층 101호</t>
+          <t>인천광역시 서구 검단로 759 2층 201, 202, 203호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rladnwjd802</t>
+          <t>https://www.instagram.com/fitnessmonth13/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1451,7 +1443,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1471,13 +1463,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>248</v>
+        <v>164</v>
       </c>
       <c r="Q11" t="n">
-        <v>245</v>
+        <v>178</v>
       </c>
       <c r="R11" t="n">
-        <v>493</v>
+        <v>342</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,12 +1478,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1947556374</t>
+          <t>1650154499</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1947556374</t>
+          <t>https://m.place.naver.com/place/1650154499</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1508,29 +1500,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>핏트레인 PT 청라</t>
+          <t>청라 피트니스비에이 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>fittrain_@naver.com</t>
+          <t>fitnessba@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1363-5598</t>
+          <t>0507-1359-0563</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 7-31 205호, 206호</t>
+          <t>인천광역시 서구 푸른로16번길 15 1층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fittrain_</t>
+          <t>https://blog.naver.com/fitnessba</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1565,13 +1557,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="Q12" t="n">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="R12" t="n">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1580,12 +1572,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1976065832</t>
+          <t>1922697320</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1976065832</t>
+          <t>https://m.place.naver.com/place/1922697320</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1597,39 +1589,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>제니의써킷짐</t>
+          <t>휘트니스칸 마전점 헬스&amp;PT&amp;골프&amp;요가&amp;필라테스</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>fcchh7023@naver.com</t>
+          <t>kann004@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1327-9857</t>
+          <t>0507-1365-4330</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉화로 52 벧엘빌딩 2층</t>
+          <t>인천광역시 서구 완정로 70 영남탑스빌아파트 상가 401호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jeny_gym2015?igsh=ZjFtOXYzYTJ2Z25l</t>
+          <t>https://fitnesskann.com/</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1639,7 +1631,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1650,7 +1642,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1659,13 +1651,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>46</v>
+        <v>1303</v>
       </c>
       <c r="Q13" t="n">
-        <v>50</v>
+        <v>608</v>
       </c>
       <c r="R13" t="n">
-        <v>96</v>
+        <v>1911</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1674,12 +1666,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1181295362</t>
+          <t>1220498447</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1181295362</t>
+          <t>https://m.place.naver.com/place/1220498447</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1696,29 +1688,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>오유짐</t>
+          <t>터닝포인트짐 헬스 PT 가좌점</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>oyugym@naver.com</t>
+          <t>turningpointgym_gajw@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1357-8173</t>
+          <t>032-576-1365</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 66 서영아너시티1차 7층 702호~704</t>
+          <t>인천광역시 서구 원적로 85 우신프라자 B1층 B01~B02호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/oyugym</t>
+          <t>https://blog.naver.com/turningpointgym_gajw</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1753,13 +1745,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>88</v>
+        <v>538</v>
       </c>
       <c r="Q14" t="n">
-        <v>93</v>
+        <v>1549</v>
       </c>
       <c r="R14" t="n">
-        <v>181</v>
+        <v>2087</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1768,12 +1760,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>576457172</t>
+          <t>1588426455</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/576457172</t>
+          <t>https://m.place.naver.com/place/1588426455</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1790,29 +1782,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>하이브짐 헬스 PT 검단점</t>
+          <t>청라스포츠센터 헬스 PT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>hivegym2021@naver.com</t>
+          <t>uzwuzw@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1491-1459</t>
+          <t>0507-1300-4100</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원당대로 841 7층 701호-704호</t>
+          <t>인천광역시 서구 청라에메랄드로 99 지젤엠 A동 4층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hivegym2021</t>
+          <t>https://www.instagram.com/csc_training_center</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1827,7 +1819,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1847,13 +1839,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3122</v>
+        <v>2834</v>
       </c>
       <c r="Q15" t="n">
-        <v>1432</v>
+        <v>1229</v>
       </c>
       <c r="R15" t="n">
-        <v>4554</v>
+        <v>4063</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1862,12 +1854,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1556816158</t>
+          <t>1213983093</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1556816158</t>
+          <t>https://m.place.naver.com/place/1213983093</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1884,29 +1876,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>더피티짐 프리미엄 루원시티점</t>
+          <t>테오짐 PT 청라점</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>gktk1877@naver.com</t>
+          <t>teogym@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1375-9681</t>
+          <t>0507-1373-7578</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오대로 270 302동 상가B 110~112호 (파리바게트 위층)</t>
+          <t>인천광역시 서구 청라커낼로 280 청라골든프라자 5층 505호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gktk1877</t>
+          <t>https://www.instagram.com/gymteogym</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1921,7 +1913,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1941,13 +1933,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="Q16" t="n">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="R16" t="n">
-        <v>299</v>
+        <v>209</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1956,12 +1948,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1650465158</t>
+          <t>1814118302</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1650465158</t>
+          <t>https://m.place.naver.com/place/1814118302</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1973,39 +1965,39 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>리커버리짐 가정점</t>
+          <t>인싸짐 가좌점 24시연중무휴 PT 헬스장</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>rcv0715@naver.com</t>
+          <t>wjdguss1045@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1393-0213</t>
+          <t>0507-1376-3818</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로110번길 7 504호</t>
+          <t>인천광역시 서구 원적로 100 지하2층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rcv0715</t>
+          <t>http://pf.kakao.com/_SxiUZG</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2015,7 +2007,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2026,7 +2018,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2035,13 +2027,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>94</v>
+        <v>1189</v>
       </c>
       <c r="Q17" t="n">
-        <v>103</v>
+        <v>748</v>
       </c>
       <c r="R17" t="n">
-        <v>197</v>
+        <v>1937</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2050,12 +2042,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1133026207</t>
+          <t>1748758798</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1133026207</t>
+          <t>https://m.place.naver.com/place/1748758798</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2072,39 +2064,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>좋은습관 PT STUDIO 청라</t>
+          <t>청라PT 바른몸피트니스 1호점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>goodhabit_ch@naver.com</t>
+          <t>barunmom_fitness@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1435-9902</t>
+          <t>0507-1340-7437</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 2층 청라PT 좋은습관</t>
+          <t>인천광역시 서구 청라루비로 93 루비타워 4층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goodhabit_ch</t>
+          <t>https://booking.naver.com/booking/12/bizes/815141</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2129,13 +2121,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>546</v>
+        <v>300</v>
       </c>
       <c r="Q18" t="n">
-        <v>259</v>
+        <v>667</v>
       </c>
       <c r="R18" t="n">
-        <v>805</v>
+        <v>967</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2144,12 +2136,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1404702049</t>
+          <t>1059514904</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1404702049</t>
+          <t>https://m.place.naver.com/place/1059514904</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2166,29 +2158,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>강자존 리햅 1대1 PT샵 루원시티점</t>
+          <t>가좌동 1:1 PT 글램핏</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>tjdwnsldlek@naver.com</t>
+          <t>glamfit_pt@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1365-0715</t>
+          <t>0507-1328-4459</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로 116 3층 306호 강자존 리햅 1대1 PT샵 루원시티점</t>
+          <t>인천광역시 서구 장고개로337번길 7 4층 401호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tjdwnsldlek/224143719751</t>
+          <t>https://open.kakao.com/o/sTCuqroe</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2203,7 +2195,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2214,22 +2206,22 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="Q19" t="n">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="R19" t="n">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2238,12 +2230,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2001611714</t>
+          <t>1111122713</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2001611714</t>
+          <t>https://m.place.naver.com/place/1111122713</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2260,29 +2252,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>청라PT&amp;몸짱스쿨</t>
+          <t>리커버리짐 가정점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>kura7792@naver.com</t>
+          <t>rcv0715@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1343-9683</t>
+          <t>0507-1393-0213</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로586번길 9-11 매그놀리아오피스텔 3층 몸짱스쿨</t>
+          <t>인천광역시 서구 봉오재3로110번길 7 504호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kura7792</t>
+          <t>https://blog.naver.com/rcv0715</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2317,13 +2309,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="Q20" t="n">
-        <v>219</v>
+        <v>103</v>
       </c>
       <c r="R20" t="n">
-        <v>329</v>
+        <v>197</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2332,12 +2324,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>37547267</t>
+          <t>1133026207</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37547267</t>
+          <t>https://m.place.naver.com/place/1133026207</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2349,34 +2341,30 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>태나핏</t>
+          <t>록 피트니스 R.O.K 헬스&amp;PT 가정점</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>anth14@naver.com</t>
+          <t>rok03903@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>032-566-7939</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 서구 승학로 515 301호, 302호, 305호</t>
+          <t>인천광역시 서구 염곡로464번길 23 엔시티타워 7층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/anth14</t>
+          <t>https://blog.naver.com/rok03903</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2407,17 +2395,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>18</v>
+        <v>727</v>
       </c>
       <c r="Q21" t="n">
-        <v>1909</v>
+        <v>1173</v>
       </c>
       <c r="R21" t="n">
-        <v>1927</v>
+        <v>1900</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2426,12 +2414,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>35623573</t>
+          <t>1475425565</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35623573</t>
+          <t>https://m.place.naver.com/place/1475425565</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2443,34 +2431,34 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>청라PT 바른몸피트니스 1호점</t>
+          <t>청년피티 청라점</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>barunmom_fitness@naver.com</t>
+          <t>cnpt3455@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1340-7437</t>
+          <t>0507-1434-3455</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로 93 루비타워 4층</t>
+          <t>인천광역시 서구 중봉대로 610 3층</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/12/bizes/815141</t>
+          <t>https://cnptoffical.qshop.ai/</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2480,12 +2468,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2505,13 +2493,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>300</v>
+        <v>434</v>
       </c>
       <c r="Q22" t="n">
-        <v>697</v>
+        <v>236</v>
       </c>
       <c r="R22" t="n">
-        <v>997</v>
+        <v>670</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2520,12 +2508,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1059514904</t>
+          <t>1293398871</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1059514904</t>
+          <t>https://m.place.naver.com/place/1293398871</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2636,29 +2624,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>데일리 무브먼트 재활&amp;PT</t>
+          <t>웰무브 근골격운동센터 청라점</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>daily_movement_@naver.com</t>
+          <t>wellmove_ex@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1491-1050</t>
+          <t>0507-1423-9397</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 60 3층 304호 데일리 무브먼트</t>
+          <t>인천광역시 서구 청라라임로 71 8층 808호, 809호 웰무브 근골격운동센터</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/daily_movement_</t>
+          <t>https://www.instagram.com/wellmove_1</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2673,7 +2661,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2693,13 +2681,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="Q24" t="n">
-        <v>42</v>
+        <v>144</v>
       </c>
       <c r="R24" t="n">
-        <v>67</v>
+        <v>196</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2708,12 +2696,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2000481326</t>
+          <t>1594642239</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2000481326</t>
+          <t>https://m.place.naver.com/place/1594642239</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2730,29 +2718,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>팀윤짐 PT 검단점</t>
+          <t>마이짐 PT 청라점</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>daalarm@naver.com</t>
+          <t>better__life@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1318-4581</t>
+          <t>0507-1378-3868</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 24 쓰리엠타워 3층 팀윤짐 검단 8호점</t>
+          <t>인천광역시 서구 중봉대로612번길 10-20 6층 마이짐</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/daalarm</t>
+          <t>https://www.instagram.com/mygym_pt_official?igsh=dGMxNWw2eG40MWtx</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2767,7 +2755,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2787,13 +2775,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>144</v>
+        <v>57</v>
       </c>
       <c r="Q25" t="n">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="R25" t="n">
-        <v>553</v>
+        <v>453</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2802,12 +2790,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1110145168</t>
+          <t>1099553298</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1110145168</t>
+          <t>https://m.place.naver.com/place/1099553298</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2824,25 +2812,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>루원짐 PT 루원시티점</t>
+          <t>제니의써킷짐</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>luwongym@naver.com</t>
+          <t>fcchh7023@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1327-9857</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청중로478번길 24 3층</t>
+          <t>인천광역시 서구 봉화로 52 벧엘빌딩 2층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/luwongym</t>
+          <t>https://www.instagram.com/jeny_gym2015?igsh=ZjFtOXYzYTJ2Z25l</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2857,7 +2849,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2877,13 +2869,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="Q26" t="n">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="R26" t="n">
-        <v>187</v>
+        <v>96</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2892,12 +2884,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1538350747</t>
+          <t>1181295362</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1538350747</t>
+          <t>https://m.place.naver.com/place/1181295362</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2909,34 +2901,34 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>위크짐 헬스&amp;PT 검단사거리점</t>
+          <t>피지컬뷰티짐 청라점 PT &amp; 헬스</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>weekgym@naver.com</t>
+          <t>physicalbeauty@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1389-7739</t>
+          <t>0507-1358-0655</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 서구 완정로 151-1 왕길빌딩 4층</t>
+          <t>인천광역시 서구 청라커낼로 270 2층 피지컬뷰티짐 청라점</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/weekgym</t>
+          <t>https://www.youtube.com/c/피지컬뷰티</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2971,13 +2963,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>268</v>
+        <v>88</v>
       </c>
       <c r="Q27" t="n">
-        <v>389</v>
+        <v>511</v>
       </c>
       <c r="R27" t="n">
-        <v>657</v>
+        <v>599</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2986,12 +2978,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1265962914</t>
+          <t>1693588410</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1265962914</t>
+          <t>https://m.place.naver.com/place/1693588410</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3003,34 +2995,34 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CM 재활PT &amp; 필라테스 검단점</t>
+          <t>어테인휘트니스 헬스&amp;PT 석남점</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jcm9909@naver.com</t>
+          <t>attain_fitness@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1334-0270</t>
+          <t>0507-1337-3765</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 34 제일프라자 405호</t>
+          <t>인천광역시 서구 길주로 101-1 투썸플레이스건물 4층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jcm9909</t>
+          <t>https://www.instagram.com/attain.fitness1/</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3045,7 +3037,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3056,7 +3048,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3065,13 +3057,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>156</v>
+        <v>355</v>
       </c>
       <c r="Q28" t="n">
-        <v>191</v>
+        <v>520</v>
       </c>
       <c r="R28" t="n">
-        <v>347</v>
+        <v>875</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3080,12 +3072,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1045251150</t>
+          <t>1639913680</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1045251150</t>
+          <t>https://m.place.naver.com/place/1639913680</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3097,34 +3089,34 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>여름필라테스 루원시티점</t>
+          <t>크로스핏 피포피 가정점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>summer3-@naver.com</t>
+          <t>bow14674@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1420-9515</t>
+          <t>0507-1345-3994</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 375 301호</t>
+          <t>인천광역시 서구 새오개로111번안길 19-1 지하 1층</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/summer3-</t>
+          <t>https://blog.naver.com/bow14674</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3159,13 +3151,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>417</v>
+        <v>55</v>
       </c>
       <c r="Q29" t="n">
-        <v>609</v>
+        <v>84</v>
       </c>
       <c r="R29" t="n">
-        <v>1026</v>
+        <v>139</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3174,12 +3166,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1993174819</t>
+          <t>1971300109</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1993174819</t>
+          <t>https://m.place.naver.com/place/1971300109</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3191,34 +3183,34 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>청라헬스장 킹짐7호점 24시 헬스 PT</t>
+          <t>엑스짐 신현점</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>kinggym7@naver.com</t>
+          <t>xgym01@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1410-9579</t>
+          <t>0507-1402-2033</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 C동 지하1층 101호</t>
+          <t>인천광역시 서구 가정로 419 . 4층 401호, 402호(신현동)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kinggym7</t>
+          <t>https://www.instagram.com/x_gym_can?igsh=NGxodHQ0b2FlbWFr</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3233,7 +3225,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3253,13 +3245,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>219</v>
+        <v>120</v>
       </c>
       <c r="Q30" t="n">
-        <v>927</v>
+        <v>430</v>
       </c>
       <c r="R30" t="n">
-        <v>1146</v>
+        <v>550</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3268,12 +3260,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2068038054</t>
+          <t>1413141073</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2068038054</t>
+          <t>https://m.place.naver.com/place/1413141073</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3290,29 +3282,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>올나잇 피트니스 가정점 헬스&amp;PT</t>
+          <t>커넥트바디 재활&amp;PT 청라점</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>rdx329@naver.com</t>
+          <t>connect-body@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1475-6636</t>
+          <t>0507-1380-8515</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 451 벨라미센텀시티2차 13층 1320호</t>
+          <t>인천광역시 서구 보석로12번안길 35 1층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/all.night_3</t>
+          <t>https://blog.naver.com/connect-body/223458723996</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3327,7 +3319,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3347,13 +3339,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1744</v>
+        <v>157</v>
       </c>
       <c r="Q31" t="n">
-        <v>536</v>
+        <v>452</v>
       </c>
       <c r="R31" t="n">
-        <v>2280</v>
+        <v>609</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3362,12 +3354,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1898172914</t>
+          <t>1346258755</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1898172914</t>
+          <t>https://m.place.naver.com/place/1346258755</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3384,29 +3376,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>힙디자인팩토리 PT 검단 신도시점</t>
+          <t>사이언스핏 PT필라 청라점</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>natural_sehun@naver.com</t>
+          <t>sciencefit@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1384-6150</t>
+          <t>0507-1487-2044</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음대로 459 파라곤프라자 3층 힙디자인팩토리</t>
+          <t>인천광역시 서구 중봉대로612번길 10-8 반안프라자 401호, 402호, 403호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/natural_sehun/223137384574</t>
+          <t>https://www.instagram.com/science_fit__</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3421,7 +3413,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3437,17 +3429,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>212</v>
+        <v>105</v>
       </c>
       <c r="Q32" t="n">
-        <v>1686</v>
+        <v>767</v>
       </c>
       <c r="R32" t="n">
-        <v>1898</v>
+        <v>872</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3456,12 +3448,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1945940640</t>
+          <t>1329193780</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1945940640</t>
+          <t>https://m.place.naver.com/place/1329193780</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3478,29 +3470,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>조스짐 2호점</t>
+          <t>레인헬스PT 서구청점</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>bonanza0917@naver.com</t>
+          <t>sonyeopps@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1417-9682</t>
+          <t>0507-1487-0787</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 437 301B동 109호 조스짐</t>
+          <t>인천광역시 서구 탁옥로 37 2층 201호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bonanza0917</t>
+          <t>https://blog.naver.com/sonyeopps</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3535,13 +3527,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="Q33" t="n">
-        <v>125</v>
+        <v>168</v>
       </c>
       <c r="R33" t="n">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3550,12 +3542,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1391522406</t>
+          <t>1799609656</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1391522406</t>
+          <t>https://m.place.naver.com/place/1799609656</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3567,44 +3559,44 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>터닝포인트짐 헬스 PT&amp;필라테스 청라점</t>
+          <t>데이온 휘트니스 헬스&amp;PT 검단1호점</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>tpgym6@naver.com</t>
+          <t>day_on11@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1340-9221</t>
+          <t>0507-1466-1299</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로 594 비전프라자 10층</t>
+          <t>인천광역시 서구 바리미로5번길 8 검단골든스퀘어 7층 전체</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.tpgymcheongna.kr</t>
+          <t>https://www.instagram.com/dayon_fitness/?hl=ko</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3620,7 +3612,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3629,13 +3621,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>417</v>
+        <v>1313</v>
       </c>
       <c r="Q34" t="n">
-        <v>3429</v>
+        <v>1049</v>
       </c>
       <c r="R34" t="n">
-        <v>3846</v>
+        <v>2362</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3644,12 +3636,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>37450365</t>
+          <t>1249225301</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37450365</t>
+          <t>https://m.place.naver.com/place/1249225301</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3666,25 +3658,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>마스터 와이짐 PT 청라점</t>
+          <t>강자존 리햅 1대1 PT샵 루원시티점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>master_y_gym@naver.com</t>
+          <t>tjdwnsldlek@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1365-0715</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로288번길 10 더스페이스타워 305호</t>
+          <t>인천광역시 서구 봉오재3로 116 3층 306호 강자존 리햅 1대1 PT샵 루원시티점</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/master__y_gym</t>
+          <t>https://blog.naver.com/tjdwnsldlek/224143719751</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3699,7 +3695,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3715,17 +3711,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>356</v>
+        <v>96</v>
       </c>
       <c r="Q35" t="n">
-        <v>494</v>
+        <v>69</v>
       </c>
       <c r="R35" t="n">
-        <v>850</v>
+        <v>165</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3734,12 +3730,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1200262369</t>
+          <t>2001611714</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1200262369</t>
+          <t>https://m.place.naver.com/place/2001611714</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3751,35 +3747,39 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>트리니티 피트니스 헬스 PT 청라</t>
+          <t>카우짐24시 서구청역점</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>trinity_fit@naver.com</t>
+          <t>coco951215@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1376-7926</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 서구 크리스탈로 84 청라 레이크가든 빌딩 5층</t>
+          <t>인천광역시 서구 탁옥로51번길 11 702호, 703호, 704호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/trinity_fit/</t>
+          <t>https://link.inpock.co.kr/cowgymseogu</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3805,17 +3805,17 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>80</v>
+        <v>1020</v>
       </c>
       <c r="Q36" t="n">
-        <v>919</v>
+        <v>324</v>
       </c>
       <c r="R36" t="n">
-        <v>999</v>
+        <v>1344</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1044334882</t>
+          <t>1106839652</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1044334882</t>
+          <t>https://m.place.naver.com/place/1106839652</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3841,39 +3841,43 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>업라이트 피트니스</t>
+          <t>터닝포인트짐</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>uprightfitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>ksmturning@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>tpgym7777@nate.com</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1392-7187</t>
+          <t>0507-1340-0803</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 서구 한들로 74 7층 업라이트 피트니스</t>
+          <t>인천광역시 서구 중봉대로 594 6층 601호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/uprightfitness</t>
+          <t>https://turningpointgym.kr/</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3903,13 +3907,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>364</v>
+        <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>453</v>
+        <v>4</v>
       </c>
       <c r="R37" t="n">
-        <v>817</v>
+        <v>5</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3918,12 +3922,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1673143477</t>
+          <t>1679398325</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1673143477</t>
+          <t>https://m.place.naver.com/place/1679398325</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -4034,29 +4038,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>청라 피트니스비에이 PT&amp;헬스</t>
+          <t>이음핏 PT 스튜디오</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>fitnessba@naver.com</t>
+          <t>eumfit@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1359-0563</t>
+          <t>0507-1433-0360</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 서구 푸른로16번길 15 1층</t>
+          <t>인천광역시 서구 서곶로 285 4층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitnessba</t>
+          <t>https://blog.naver.com/eumfit</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4091,13 +4095,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="Q39" t="n">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="R39" t="n">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4106,12 +4110,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1922697320</t>
+          <t>1260849924</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1922697320</t>
+          <t>https://m.place.naver.com/place/1260849924</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4123,34 +4127,34 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>크로스핏 피포피 가정점</t>
+          <t>힙디자인팩토리 PT 검단 신도시점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>bow14674@naver.com</t>
+          <t>natural_sehun@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1345-3994</t>
+          <t>0507-1384-6150</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 서구 새오개로111번안길 19-1 지하 1층</t>
+          <t>인천광역시 서구 이음대로 459 파라곤프라자 3층 힙디자인팩토리</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bow14674</t>
+          <t>https://blog.naver.com/natural_sehun/223137384574</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4181,17 +4185,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>55</v>
+        <v>212</v>
       </c>
       <c r="Q40" t="n">
-        <v>84</v>
+        <v>1686</v>
       </c>
       <c r="R40" t="n">
-        <v>139</v>
+        <v>1898</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4200,12 +4204,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1971300109</t>
+          <t>1945940640</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1971300109</t>
+          <t>https://m.place.naver.com/place/1945940640</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4222,25 +4226,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>마침.여기,피티스튜디오</t>
+          <t>핏트레인 PT 청라</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>su2kimc@naver.com</t>
+          <t>fittrain_@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1363-5598</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음대로 388 ABM타워 3층 303호</t>
+          <t>인천광역시 서구 청라한내로72번길 7-31 205호, 206호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/su2kimc</t>
+          <t>https://blog.naver.com/fittrain_</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4275,13 +4283,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>94</v>
+        <v>49</v>
       </c>
       <c r="Q41" t="n">
-        <v>342</v>
+        <v>86</v>
       </c>
       <c r="R41" t="n">
-        <v>436</v>
+        <v>135</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4290,12 +4298,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1381559698</t>
+          <t>1976065832</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1381559698</t>
+          <t>https://m.place.naver.com/place/1976065832</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4312,25 +4320,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>록 피트니스 R.O.K 헬스&amp;PT 가정점</t>
+          <t>플러스짐 24시 헬스 PT 검단점</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>rok03903@naver.com</t>
+          <t>plusgymgeomdan@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1362-0454</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로464번길 23 엔시티타워 7층</t>
+          <t>인천광역시 서구 검단로 455 검단KB빌딩 3층 301, 302호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rok03903</t>
+          <t>https://blog.naver.com/plusgymgeomdan</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4356,7 +4368,7 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4365,13 +4377,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>727</v>
+        <v>529</v>
       </c>
       <c r="Q42" t="n">
-        <v>1173</v>
+        <v>618</v>
       </c>
       <c r="R42" t="n">
-        <v>1900</v>
+        <v>1147</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4380,12 +4392,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1475425565</t>
+          <t>2090890779</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1475425565</t>
+          <t>https://m.place.naver.com/place/2090890779</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4402,34 +4414,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>레인헬스PT 서구청점</t>
+          <t>피타짐 서구청역점 24시 헬스PT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>sonyeopps@naver.com</t>
+          <t>fita_07@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1487-0787</t>
+          <t>0507-1389-6929</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 서구 탁옥로 37 2층 201호</t>
+          <t>인천광역시 서구 탁옥로98번길 1 4층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sonyeopps</t>
+          <t>http://pf.kakao.com/_Sraxin/chat</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4439,7 +4451,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4450,7 +4462,7 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4459,13 +4471,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="Q43" t="n">
-        <v>168</v>
+        <v>132</v>
       </c>
       <c r="R43" t="n">
-        <v>293</v>
+        <v>215</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4474,12 +4486,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1799609656</t>
+          <t>2094767341</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1799609656</t>
+          <t>https://m.place.naver.com/place/2094767341</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4556,10 +4568,10 @@
         <v>86</v>
       </c>
       <c r="Q44" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="R44" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4590,29 +4602,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>찐바디핏</t>
+          <t>태나핏</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>din32@naver.com</t>
+          <t>anth14@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1377-4737</t>
+          <t>032-566-7939</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 서구 크리스탈로 78 엘림존 301호</t>
+          <t>인천광역시 서구 승학로 515 301호, 302호, 305호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/din32</t>
+          <t>https://blog.naver.com/anth14</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4643,17 +4655,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>146</v>
+        <v>18</v>
       </c>
       <c r="Q45" t="n">
-        <v>443</v>
+        <v>1910</v>
       </c>
       <c r="R45" t="n">
-        <v>589</v>
+        <v>1928</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4662,12 +4674,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1039953052</t>
+          <t>35623573</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1039953052</t>
+          <t>https://m.place.naver.com/place/35623573</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4684,29 +4696,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>피지컬뷰티짐 청라점 PT &amp; 헬스</t>
+          <t>더피티짐 헬스&amp;PT 검단점</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>physicalbeauty@naver.com</t>
+          <t>volleystar1@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1358-0655</t>
+          <t>0507-1448-1037</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로 270 2층 피지컬뷰티짐 청라점</t>
+          <t>인천광역시 서구 이음대로 463 센트럴시티 4층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/c/피지컬뷰티</t>
+          <t>https://thepit.creatorlink.net</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4732,7 +4744,7 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4741,13 +4753,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>88</v>
+        <v>240</v>
       </c>
       <c r="Q46" t="n">
-        <v>511</v>
+        <v>266</v>
       </c>
       <c r="R46" t="n">
-        <v>599</v>
+        <v>506</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4756,12 +4768,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1693588410</t>
+          <t>1631976018</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1693588410</t>
+          <t>https://m.place.naver.com/place/1631976018</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4773,34 +4785,34 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>클래식짐청라PT</t>
+          <t>청라헬스장 킹짐7호점 24시 헬스 PT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>classicgym-@naver.com</t>
+          <t>kinggym7@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1350-6909</t>
+          <t>0507-1410-9579</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로161번길 1 2층</t>
+          <t>인천광역시 서구 청라라임로 85 C동 지하1층 101호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/kinggym7</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4810,12 +4822,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4831,17 +4843,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>27</v>
+        <v>219</v>
       </c>
       <c r="Q47" t="n">
-        <v>2</v>
+        <v>928</v>
       </c>
       <c r="R47" t="n">
-        <v>29</v>
+        <v>1147</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4850,12 +4862,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2057021183</t>
+          <t>2068038054</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2057021183</t>
+          <t>https://m.place.naver.com/place/2068038054</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4867,34 +4879,34 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>어테인휘트니스 헬스&amp;PT 석남점</t>
+          <t>터닝포인트짐 헬스 PT&amp;필라테스 청라점</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>attain_fitness@naver.com</t>
+          <t>tpgym6@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1337-3765</t>
+          <t>0507-1340-9221</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 서구 길주로 101-1 투썸플레이스건물 4층</t>
+          <t>인천광역시 서구 중봉대로 594 비전프라자 10층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/attain.fitness1/</t>
+          <t>https://www.tpgymcheongna.kr</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4904,12 +4916,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4929,13 +4941,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>353</v>
+        <v>417</v>
       </c>
       <c r="Q48" t="n">
-        <v>519</v>
+        <v>3428</v>
       </c>
       <c r="R48" t="n">
-        <v>872</v>
+        <v>3845</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4944,12 +4956,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1639913680</t>
+          <t>37450365</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1639913680</t>
+          <t>https://m.place.naver.com/place/37450365</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4966,29 +4978,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>펌퍼스짐 헬스&amp;PT 청라</t>
+          <t>하루50분 PT필라테스 청라점</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>pumper_gym@naver.com</t>
+          <t>rladnwjd802@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1476-9054</t>
+          <t>0507-1311-9363</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로 110 파이낸스센터 6층</t>
+          <t>인천광역시 서구 청라라임로122번길 16-1 1층 101호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pumpers_gym?igsh=MXJueDAwamF5cWpheQ%3D%3D&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/rladnwjd802</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5003,7 +5015,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5023,13 +5035,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="Q49" t="n">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="R49" t="n">
-        <v>514</v>
+        <v>493</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5038,12 +5050,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1828279952</t>
+          <t>1947556374</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1828279952</t>
+          <t>https://m.place.naver.com/place/1947556374</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5055,34 +5067,34 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>엘핏 청라점</t>
+          <t>위크짐 헬스&amp;PT 검단사거리점</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>lemongym-cn@naver.com</t>
+          <t>weekgym@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1428-5104</t>
+          <t>0507-1389-7739</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 서구 옥빛로13번길 3 1층 엘핏</t>
+          <t>인천광역시 서구 완정로 151-1 왕길빌딩 4층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lemongym-cn</t>
+          <t>https://blog.naver.com/weekgym</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5117,13 +5129,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>65</v>
+        <v>269</v>
       </c>
       <c r="Q50" t="n">
-        <v>89</v>
+        <v>390</v>
       </c>
       <c r="R50" t="n">
-        <v>154</v>
+        <v>659</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5132,12 +5144,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1196898702</t>
+          <t>1265962914</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1196898702</t>
+          <t>https://m.place.naver.com/place/1265962914</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5154,29 +5166,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>터닝포인트짐 헬스 PT 가좌점</t>
+          <t>세인트피트니스 청라점 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>turningpointgym_gajw@naver.com</t>
+          <t>soccerkkw2@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>032-576-1365</t>
+          <t>0507-1354-4659</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원적로 85 우신프라자 B1층 B01~B02호</t>
+          <t>인천광역시 서구 청라라임로 71 진영메디피아 9층 905호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/turningpointgym_gajw</t>
+          <t>https://blog.naver.com/soccerkkw2</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5211,13 +5223,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>538</v>
+        <v>948</v>
       </c>
       <c r="Q51" t="n">
-        <v>1549</v>
+        <v>916</v>
       </c>
       <c r="R51" t="n">
-        <v>2087</v>
+        <v>1864</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5226,12 +5238,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1588426455</t>
+          <t>1577621981</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1588426455</t>
+          <t>https://m.place.naver.com/place/1577621981</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5248,29 +5260,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>데이온 휘트니스 헬스&amp;PT 검단1호점</t>
+          <t>하이브짐 헬스 PT 검단점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>day_on11@naver.com</t>
+          <t>hivegym2021@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1466-1299</t>
+          <t>0507-1491-1459</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 서구 바리미로5번길 8 검단골든스퀘어 7층 전체</t>
+          <t>인천광역시 서구 원당대로 841 7층 701호-704호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dayon_fitness/?hl=ko</t>
+          <t>https://blog.naver.com/hivegym2021</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5285,7 +5297,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5305,13 +5317,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1312</v>
+        <v>3122</v>
       </c>
       <c r="Q52" t="n">
-        <v>1058</v>
+        <v>1432</v>
       </c>
       <c r="R52" t="n">
-        <v>2370</v>
+        <v>4554</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5320,12 +5332,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1249225301</t>
+          <t>1556816158</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1249225301</t>
+          <t>https://m.place.naver.com/place/1556816158</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5342,29 +5354,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>젠틀레이디짐 PT&amp;필라테스</t>
+          <t>팀윤짐 PT 검단점</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>gentlelady_gym@naver.com</t>
+          <t>daalarm@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1384-8303</t>
+          <t>0507-1318-4581</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로288번길 26 상가동 103동 324호</t>
+          <t>인천광역시 서구 이음5로 24 쓰리엠타워 3층 팀윤짐 검단 8호점</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gentlelady_gym</t>
+          <t>https://blog.naver.com/daalarm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5399,13 +5411,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>532</v>
+        <v>145</v>
       </c>
       <c r="Q53" t="n">
-        <v>620</v>
+        <v>409</v>
       </c>
       <c r="R53" t="n">
-        <v>1152</v>
+        <v>554</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5414,12 +5426,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1188954884</t>
+          <t>1110145168</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1188954884</t>
+          <t>https://m.place.naver.com/place/1110145168</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5436,29 +5448,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>피트니스13월 불로점</t>
+          <t>클래식짐청라PT</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>fitnessmonth13@naver.com</t>
+          <t>classicgym-@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1480-3383</t>
+          <t>0507-1350-6909</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 서구 검단로 759 2층 201, 202, 203호</t>
+          <t>인천광역시 서구 청라한내로161번길 1 2층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fitnessmonth13/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5468,7 +5480,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5489,17 +5501,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>164</v>
+        <v>27</v>
       </c>
       <c r="Q54" t="n">
-        <v>178</v>
+        <v>2</v>
       </c>
       <c r="R54" t="n">
-        <v>342</v>
+        <v>29</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5508,12 +5520,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1650154499</t>
+          <t>2057021183</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1650154499</t>
+          <t>https://m.place.naver.com/place/2057021183</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5525,34 +5537,34 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5150피트니스 헬스&amp;필라테스&amp;PT 검단점</t>
+          <t>여름필라테스 루원시티점</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>jgym0202@naver.com</t>
+          <t>summer3-@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1413-1819</t>
+          <t>0507-1420-9515</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 서구 서곶로 788 홀리랜드 3층 5150피트니스 검단점</t>
+          <t>인천광역시 서구 가정로 375 301호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jgym0202</t>
+          <t>https://blog.naver.com/summer3-</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5587,13 +5599,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>562</v>
+        <v>418</v>
       </c>
       <c r="Q55" t="n">
-        <v>1525</v>
+        <v>609</v>
       </c>
       <c r="R55" t="n">
-        <v>2087</v>
+        <v>1027</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5602,12 +5614,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>37434686</t>
+          <t>1993174819</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37434686</t>
+          <t>https://m.place.naver.com/place/1993174819</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5619,39 +5631,35 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>카우짐24시 서구청역점</t>
+          <t>루원짐 PT 루원시티점</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>coco951215@naver.com</t>
+          <t>luwongym@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>0507-1376-7926</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 서구 탁옥로51번길 11 702호, 703호, 704호</t>
+          <t>인천광역시 서구 청중로478번길 24 3층</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/cowgymseogu</t>
+          <t>https://blog.naver.com/luwongym</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5677,17 +5685,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1020</v>
+        <v>77</v>
       </c>
       <c r="Q56" t="n">
-        <v>324</v>
+        <v>110</v>
       </c>
       <c r="R56" t="n">
-        <v>1344</v>
+        <v>187</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5696,12 +5704,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1106839652</t>
+          <t>1538350747</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1106839652</t>
+          <t>https://m.place.naver.com/place/1538350747</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5713,34 +5721,34 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>드라이짐 헬스&amp;PT 검단점</t>
+          <t>더피티짐 프리미엄 루원시티점</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>drygym@naver.com</t>
+          <t>gktk1877@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1350-0887</t>
+          <t>0507-1375-9681</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 서구 이음5로 72 국제프라자 7층 드라이짐</t>
+          <t>인천광역시 서구 봉오대로 270 302동 상가B 110~112호 (파리바게트 위층)</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/drygym</t>
+          <t>https://blog.naver.com/gktk1877</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5775,13 +5783,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1523</v>
+        <v>121</v>
       </c>
       <c r="Q57" t="n">
-        <v>1389</v>
+        <v>179</v>
       </c>
       <c r="R57" t="n">
-        <v>2912</v>
+        <v>300</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5790,12 +5798,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1566516040</t>
+          <t>1650465158</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1566516040</t>
+          <t>https://m.place.naver.com/place/1650465158</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5812,34 +5820,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>피타짐 서구청역점 24시 헬스PT</t>
+          <t>고트트레이닝센터</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>fita_07@naver.com</t>
+          <t>goat_psvt@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1389-6929</t>
+          <t>0507-1330-9573</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 서구 탁옥로98번길 1 4층</t>
+          <t>인천광역시 서구 서곶로 746 3층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Sraxin/chat</t>
+          <t>https://blog.naver.com/goat_psvt</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5849,7 +5857,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5860,22 +5868,22 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="Q58" t="n">
-        <v>132</v>
+        <v>276</v>
       </c>
       <c r="R58" t="n">
-        <v>215</v>
+        <v>294</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5884,12 +5892,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>2094767341</t>
+          <t>1362765821</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2094767341</t>
+          <t>https://m.place.naver.com/place/1362765821</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5906,29 +5914,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>하루50분 PT필라테스 청라4호점</t>
+          <t>프레임짐 헬스 PT 검단</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>rladnwjd802@naver.com</t>
+          <t>framegym_yu@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1423-7258</t>
+          <t>0507-1352-9688</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 78 4층 405호</t>
+          <t>인천광역시 서구 검단로 480 리치웰프라자 10층 프레임짐</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rladnwjd802</t>
+          <t>https://blog.naver.com/framegym_yu</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5963,13 +5971,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>129</v>
+        <v>92</v>
       </c>
       <c r="Q59" t="n">
-        <v>123</v>
+        <v>318</v>
       </c>
       <c r="R59" t="n">
-        <v>252</v>
+        <v>410</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5978,12 +5986,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>2038838362</t>
+          <t>1741458759</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038838362</t>
+          <t>https://m.place.naver.com/place/1741458759</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6000,29 +6008,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>이음핏 PT 스튜디오</t>
+          <t>펌퍼스짐 헬스&amp;PT 청라</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>eumfit@naver.com</t>
+          <t>pumper_gym@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1433-0360</t>
+          <t>0507-1476-9054</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 서구 서곶로 285 4층</t>
+          <t>인천광역시 서구 청라한내로 110 파이낸스센터 6층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/eumfit</t>
+          <t>https://www.instagram.com/pumpers_gym?igsh=MXJueDAwamF5cWpheQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6037,7 +6045,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6057,13 +6065,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>100</v>
+        <v>257</v>
       </c>
       <c r="Q60" t="n">
-        <v>41</v>
+        <v>263</v>
       </c>
       <c r="R60" t="n">
-        <v>141</v>
+        <v>520</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6072,12 +6080,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1260849924</t>
+          <t>1828279952</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1260849924</t>
+          <t>https://m.place.naver.com/place/1828279952</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6089,34 +6097,34 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1:1 개인PT샵 팻번</t>
+          <t>업라이트 피트니스</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>gbw21@naver.com</t>
+          <t>uprightfitness@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>032-246-2158</t>
+          <t>0507-1392-7187</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 서구 건지로 375 5층 팻번</t>
+          <t>인천광역시 서구 한들로 74 7층 업라이트 피트니스</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gbw21</t>
+          <t>https://blog.naver.com/uprightfitness</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6151,13 +6159,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>148</v>
+        <v>364</v>
       </c>
       <c r="Q61" t="n">
-        <v>260</v>
+        <v>463</v>
       </c>
       <c r="R61" t="n">
-        <v>408</v>
+        <v>827</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6166,12 +6174,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1216515131</t>
+          <t>1673143477</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1216515131</t>
+          <t>https://m.place.naver.com/place/1673143477</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6183,39 +6191,39 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>청년피티 청라점</t>
+          <t>엘핏 청라점</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>cnpt3455@naver.com</t>
+          <t>lemongym-cn@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1434-3455</t>
+          <t>0507-1428-5104</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로 610 3층</t>
+          <t>인천광역시 서구 옥빛로13번길 3 1층 엘핏</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://cnptoffical.qshop.ai/</t>
+          <t>https://blog.naver.com/lemongym-cn</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6225,7 +6233,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6245,13 +6253,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>433</v>
+        <v>65</v>
       </c>
       <c r="Q62" t="n">
-        <v>236</v>
+        <v>89</v>
       </c>
       <c r="R62" t="n">
-        <v>669</v>
+        <v>154</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6260,12 +6268,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1293398871</t>
+          <t>1196898702</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1293398871</t>
+          <t>https://m.place.naver.com/place/1196898702</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6277,34 +6285,30 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>머슬피플 피트니스 헬스 PT 청라</t>
+          <t>마침.여기,피티스튜디오</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>kdkkdk8399@naver.com</t>
+          <t>su2kimc@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>0507-1339-0000</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 23 701호, 702호</t>
+          <t>인천광역시 서구 이음대로 388 ABM타워 3층 303호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kdkkdk8399</t>
+          <t>https://blog.naver.com/su2kimc</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6339,13 +6343,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>370</v>
+        <v>94</v>
       </c>
       <c r="Q63" t="n">
-        <v>1162</v>
+        <v>342</v>
       </c>
       <c r="R63" t="n">
-        <v>1532</v>
+        <v>436</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6354,12 +6358,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1197174862</t>
+          <t>1381559698</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1197174862</t>
+          <t>https://m.place.naver.com/place/1381559698</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6376,39 +6380,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>바디소나타 헬스 PT 청라</t>
+          <t>검단플렉스짐PT 완정점</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>body_sonata@naver.com</t>
+          <t>flexpt@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1404-7217</t>
+          <t>0507-1328-8130</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로586번길 15 청연프라자 10층</t>
+          <t>인천광역시 서구 원당대로 676 3층 304호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://2080ttt.wixsite.com/bodysonata</t>
+          <t>https://m.blog.naver.com/PostList.nhn?blogId=flexpt</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6429,17 +6433,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1580</v>
+        <v>80</v>
       </c>
       <c r="Q64" t="n">
-        <v>1579</v>
+        <v>1269</v>
       </c>
       <c r="R64" t="n">
-        <v>3159</v>
+        <v>1349</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6448,12 +6452,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>38782467</t>
+          <t>1127062086</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38782467</t>
+          <t>https://m.place.naver.com/place/1127062086</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6465,39 +6469,39 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>휘트니스칸 헬스&amp;PT&amp;골프&amp;요가&amp;필라테스 마전점</t>
+          <t>1:1 개인PT샵 팻번</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>kann004@naver.com</t>
+          <t>gbw21@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1365-4330</t>
+          <t>032-246-2158</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 서구 완정로 70 영남탑스빌아파트 상가 401호</t>
+          <t>인천광역시 서구 건지로 375 5층 팻번</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://fitnesskann.com/</t>
+          <t>https://blog.naver.com/gbw21</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6518,7 +6522,7 @@
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -6527,13 +6531,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1301</v>
+        <v>148</v>
       </c>
       <c r="Q65" t="n">
-        <v>610</v>
+        <v>260</v>
       </c>
       <c r="R65" t="n">
-        <v>1911</v>
+        <v>408</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6542,12 +6546,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1220498447</t>
+          <t>1216515131</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1220498447</t>
+          <t>https://m.place.naver.com/place/1216515131</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6564,29 +6568,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>세인트피트니스 청라점 PT&amp;헬스</t>
+          <t>오유짐</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>soccerkkw2@naver.com</t>
+          <t>oyugym@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1354-4659</t>
+          <t>0507-1357-8173</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 71 진영메디피아 9층 905호</t>
+          <t>인천광역시 서구 이음5로 66 서영아너시티1차 7층 702호~704</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/soccerkkw2</t>
+          <t>https://blog.naver.com/oyugym</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6621,13 +6625,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>948</v>
+        <v>88</v>
       </c>
       <c r="Q66" t="n">
-        <v>916</v>
+        <v>93</v>
       </c>
       <c r="R66" t="n">
-        <v>1864</v>
+        <v>181</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6636,12 +6640,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1577621981</t>
+          <t>576457172</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1577621981</t>
+          <t>https://m.place.naver.com/place/576457172</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6653,34 +6657,34 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>엑스짐 신현점</t>
+          <t>5150피트니스 헬스&amp;필라테스&amp;PT 검단점</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>xgym01@naver.com</t>
+          <t>jgym0202@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1402-2033</t>
+          <t>0507-1413-1819</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 419 . 4층 401호, 402호(신현동)</t>
+          <t>인천광역시 서구 서곶로 788 홀리랜드 3층 5150피트니스 검단점</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/x_gym_can?igsh=NGxodHQ0b2FlbWFr</t>
+          <t>https://blog.naver.com/jgym0202</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6695,7 +6699,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6715,13 +6719,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>120</v>
+        <v>562</v>
       </c>
       <c r="Q67" t="n">
-        <v>430</v>
+        <v>1525</v>
       </c>
       <c r="R67" t="n">
-        <v>550</v>
+        <v>2087</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6730,12 +6734,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1413141073</t>
+          <t>37434686</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1413141073</t>
+          <t>https://m.place.naver.com/place/37434686</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6747,34 +6751,34 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>마이짐 PT 청라점</t>
+          <t>드라이짐 헬스&amp;PT 검단점</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>better__life@naver.com</t>
+          <t>drygym@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1378-3868</t>
+          <t>0507-1350-0887</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로612번길 10-20 6층 마이짐</t>
+          <t>인천광역시 서구 이음5로 72 국제프라자 7층 드라이짐</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mygym_pt_official?igsh=dGMxNWw2eG40MWtx</t>
+          <t>https://blog.naver.com/drygym</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6789,7 +6793,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6809,13 +6813,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>57</v>
+        <v>1523</v>
       </c>
       <c r="Q68" t="n">
-        <v>396</v>
+        <v>1390</v>
       </c>
       <c r="R68" t="n">
-        <v>453</v>
+        <v>2913</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6824,12 +6828,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1099553298</t>
+          <t>1566516040</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1099553298</t>
+          <t>https://m.place.naver.com/place/1566516040</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6846,29 +6850,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>사이언스핏 PT필라 청라점</t>
+          <t>청라PT&amp;몸짱스쿨</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>sciencefit@naver.com</t>
+          <t>kura7792@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1487-2044</t>
+          <t>0507-1343-9683</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로612번길 10-8 반안프라자 401호, 402호, 403호</t>
+          <t>인천광역시 서구 중봉대로586번길 9-11 매그놀리아오피스텔 3층 몸짱스쿨</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/science_fit__</t>
+          <t>https://blog.naver.com/kura7792</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6883,7 +6887,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6903,13 +6907,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="Q69" t="n">
-        <v>762</v>
+        <v>219</v>
       </c>
       <c r="R69" t="n">
-        <v>867</v>
+        <v>329</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6918,12 +6922,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1329193780</t>
+          <t>37547267</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1329193780</t>
+          <t>https://m.place.naver.com/place/37547267</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -6940,29 +6944,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>고트트레이닝센터</t>
+          <t>CM 재활PT &amp; 필라테스 검단점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>goat_psvt@naver.com</t>
+          <t>jcm9909@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1330-9573</t>
+          <t>0507-1334-0270</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 서구 서곶로 746 3층</t>
+          <t>인천광역시 서구 이음5로 34 제일프라자 405호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goat_psvt</t>
+          <t>https://blog.naver.com/jcm9909</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6993,17 +6997,17 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>18</v>
+        <v>156</v>
       </c>
       <c r="Q70" t="n">
-        <v>276</v>
+        <v>191</v>
       </c>
       <c r="R70" t="n">
-        <v>294</v>
+        <v>347</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7012,12 +7016,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1362765821</t>
+          <t>1045251150</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1362765821</t>
+          <t>https://m.place.naver.com/place/1045251150</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7029,34 +7033,34 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>청라스포츠센터 헬스 PT</t>
+          <t>하루50분 PT필라테스 루원시티점</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>uzwuzw@naver.com</t>
+          <t>rladnwjd802@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1300-4100</t>
+          <t>0507-1481-4556</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 99 지젤엠 A동 4층</t>
+          <t>인천광역시 서구 봉오대로 255 눈담봄 5층 507,8호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/csc_training_center</t>
+          <t>https://blog.naver.com/rladnwjd802</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7071,7 +7075,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7091,13 +7095,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2832</v>
+        <v>226</v>
       </c>
       <c r="Q71" t="n">
-        <v>1229</v>
+        <v>195</v>
       </c>
       <c r="R71" t="n">
-        <v>4061</v>
+        <v>421</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7106,12 +7110,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1213983093</t>
+          <t>1001087379</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213983093</t>
+          <t>https://m.place.naver.com/place/1001087379</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7128,34 +7132,34 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>플러스짐 24시 헬스 PT 검단점</t>
+          <t>GN짐 헬스&amp;PT 검단점</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>plusgymgeomdan@naver.com</t>
+          <t>gn_gym-@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1362-0454</t>
+          <t>0507-1458-7938</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 서구 검단로 455 검단KB빌딩 3층 301, 302호</t>
+          <t>인천광역시 서구 완정로 148-1 6층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/plusgymgeomdan</t>
+          <t>https://pf.kakao.com/_tkdBn</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7165,7 +7169,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7185,13 +7189,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>528</v>
+        <v>125</v>
       </c>
       <c r="Q72" t="n">
-        <v>617</v>
+        <v>583</v>
       </c>
       <c r="R72" t="n">
-        <v>1145</v>
+        <v>708</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7200,12 +7204,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>2090890779</t>
+          <t>2036025124</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2090890779</t>
+          <t>https://m.place.naver.com/place/2036025124</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7222,29 +7226,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>가좌동 1:1 PT 글램핏</t>
+          <t>청라PT 바른몸피트니스 2호점</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>glamfit_pt@naver.com</t>
+          <t>barunmom_fitness@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1328-4459</t>
+          <t>0507-1413-7437</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 서구 장고개로337번길 7 4층 401호</t>
+          <t>인천광역시 서구 중봉대로612번길 10-22 604, 605호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sTCuqroe</t>
+          <t>https://booking.naver.com/booking/12/bizes/1418130</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7254,7 +7258,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -7270,7 +7274,7 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7279,13 +7283,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q73" t="n">
-        <v>112</v>
+        <v>213</v>
       </c>
       <c r="R73" t="n">
-        <v>188</v>
+        <v>288</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7294,12 +7298,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1111122713</t>
+          <t>2032271782</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1111122713</t>
+          <t>https://m.place.naver.com/place/2032271782</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7311,39 +7315,39 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GN짐 헬스&amp;PT 검단점</t>
+          <t>데일리 무브먼트 재활&amp;PT</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>gn_gym-@naver.com</t>
+          <t>daily_movement_@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1458-7938</t>
+          <t>0507-1491-1050</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>인천광역시 서구 완정로 148-1 6층</t>
+          <t>인천광역시 서구 이음5로 60 3층 304호 데일리 무브먼트</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_tkdBn</t>
+          <t>https://blog.naver.com/daily_movement_</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7353,7 +7357,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7364,7 +7368,7 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7373,13 +7377,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="Q74" t="n">
-        <v>581</v>
+        <v>43</v>
       </c>
       <c r="R74" t="n">
-        <v>706</v>
+        <v>68</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7388,12 +7392,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>2036025124</t>
+          <t>2000481326</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2036025124</t>
+          <t>https://m.place.naver.com/place/2000481326</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7410,39 +7414,35 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>청라PT 바른몸피트니스 2호점</t>
+          <t>마스터 와이짐 PT 청라점</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>barunmom_fitness@naver.com</t>
+          <t>master_y_gym@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>0507-1413-7437</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로612번길 10-22 604, 605호</t>
+          <t>인천광역시 서구 청라커낼로288번길 10 더스페이스타워 305호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/12/bizes/1418130</t>
+          <t>https://www.instagram.com/master__y_gym</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7467,13 +7467,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>75</v>
+        <v>356</v>
       </c>
       <c r="Q75" t="n">
-        <v>213</v>
+        <v>494</v>
       </c>
       <c r="R75" t="n">
-        <v>288</v>
+        <v>850</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7482,12 +7482,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>2032271782</t>
+          <t>1200262369</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2032271782</t>
+          <t>https://m.place.naver.com/place/1200262369</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -7504,29 +7504,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>커넥트바디 재활&amp;PT 청라점</t>
+          <t>조스짐 2호점</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>connect-body@naver.com</t>
+          <t>bonanza0917@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1380-8515</t>
+          <t>0507-1417-9682</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>인천광역시 서구 보석로12번안길 35 1층</t>
+          <t>인천광역시 서구 가정로 437 301B동 109호 조스짐</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/connect-body/223458723996</t>
+          <t>https://blog.naver.com/bonanza0917</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="Q76" t="n">
-        <v>451</v>
+        <v>126</v>
       </c>
       <c r="R76" t="n">
-        <v>608</v>
+        <v>277</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7576,12 +7576,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1346258755</t>
+          <t>1391522406</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1346258755</t>
+          <t>https://m.place.naver.com/place/1391522406</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
